--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Edad-trans_bre.xlsx
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,11; 5,17</t>
+          <t>1,19; 5,39</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,52; 7,74</t>
+          <t>2,01; 7,79</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2,49; 16,07</t>
+          <t>3,22; 16,35</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>23,8; 1698,1</t>
+          <t>41,88; 1736,78</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>78,2; 1036,41</t>
+          <t>51,5; 984,48</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>7,52; 631,76</t>
+          <t>23,29; 618,58</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,83; 6,02</t>
+          <t>0,99; 6,2</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,62; 5,85</t>
+          <t>0,72; 5,65</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,07; 10,57</t>
+          <t>1,01; 11,01</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,03; 219,25</t>
+          <t>18,18; 234,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,15; 287,83</t>
+          <t>7,86; 271,26</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>8,83; 246,0</t>
+          <t>13,02; 273,33</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,89; 13,89</t>
+          <t>6,91; 13,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,54; 8,02</t>
+          <t>1,42; 7,53</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,2; 11,66</t>
+          <t>2,92; 11,74</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>100,24; 326,73</t>
+          <t>93,73; 311,66</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,49; 190,95</t>
+          <t>20,65; 179,91</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>32,67; 161,61</t>
+          <t>26,93; 166,91</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,22; 14,1</t>
+          <t>5,16; 14,33</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,22; 12,23</t>
+          <t>3,52; 11,93</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,18; 22,99</t>
+          <t>7,17; 25,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>34,01; 133,8</t>
+          <t>30,25; 126,87</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>20,0; 102,84</t>
+          <t>23,73; 100,33</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,35; 366,83</t>
+          <t>37,06; 360,68</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,61; 25,84</t>
+          <t>12,49; 26,01</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,17; 21,34</t>
+          <t>9,36; 21,38</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,24; 16,34</t>
+          <t>7,29; 16,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>45,0; 114,34</t>
+          <t>42,79; 116,32</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,49; 103,86</t>
+          <t>34,52; 105,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>23,45; 66,34</t>
+          <t>24,26; 68,63</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,08; 19,08</t>
+          <t>3,31; 19,27</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,71; 26,66</t>
+          <t>11,76; 26,61</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-17,23; 20,05</t>
+          <t>-16,17; 19,89</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,49; 41,89</t>
+          <t>6,02; 42,08</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>30,7; 88,16</t>
+          <t>31,61; 89,48</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-55,65; 73,54</t>
+          <t>-53,22; 71,66</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>4,9; 20,22</t>
+          <t>5,03; 19,38</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>4,0; 19,61</t>
+          <t>3,86; 19,6</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,05; 30,59</t>
+          <t>19,73; 31,58</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6,96; 33,32</t>
+          <t>7,07; 31,84</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>7,46; 42,71</t>
+          <t>6,84; 41,59</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>39,2; 76,45</t>
+          <t>42,65; 82,22</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,24; 14,28</t>
+          <t>10,23; 14,16</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,98; 12,76</t>
+          <t>8,87; 12,86</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,28; 16,01</t>
+          <t>7,17; 15,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,77; 87,87</t>
+          <t>56,82; 88,56</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>56,81; 89,65</t>
+          <t>55,23; 91,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>43,15; 110,98</t>
+          <t>41,82; 109,93</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/POLIPATOLOGIA_Lim_2-Edad-trans_bre.xlsx
+++ b/data/trans_bre/POLIPATOLOGIA_Lim_2-Edad-trans_bre.xlsx
@@ -606,7 +606,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>9,11</t>
+          <t>10,14</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -621,7 +621,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>197,27%</t>
+          <t>231,06%</t>
         </is>
       </c>
     </row>
@@ -634,32 +634,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 5,39</t>
+          <t>1,08; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2,01; 7,79</t>
+          <t>2,21; 7,52</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,22; 16,35</t>
+          <t>4,12; 17,2</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>41,88; 1736,78</t>
+          <t>41,28; 1695,85</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,5; 984,48</t>
+          <t>49,43; 995,52</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,29; 618,58</t>
+          <t>40,01; 802,66</t>
         </is>
       </c>
     </row>
@@ -686,7 +686,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6,33</t>
+          <t>7,49</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -701,7 +701,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>106,56%</t>
+          <t>126,58%</t>
         </is>
       </c>
     </row>
@@ -714,32 +714,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,99; 6,2</t>
+          <t>0,76; 5,88</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,72; 5,65</t>
+          <t>0,66; 5,56</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1,01; 11,01</t>
+          <t>3,15; 11,6</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>18,18; 234,78</t>
+          <t>15,48; 214,94</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,86; 271,26</t>
+          <t>13,2; 262,6</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,02; 273,33</t>
+          <t>36,32; 309,26</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7,97</t>
+          <t>10,3</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>90,68%</t>
+          <t>124,03%</t>
         </is>
       </c>
     </row>
@@ -794,32 +794,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6,91; 13,61</t>
+          <t>6,35; 13,39</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,42; 7,53</t>
+          <t>1,8; 7,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2,92; 11,74</t>
+          <t>7,07; 13,77</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>93,73; 311,66</t>
+          <t>86,99; 318,48</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>20,65; 179,91</t>
+          <t>24,22; 172,92</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>26,93; 166,91</t>
+          <t>65,55; 207,86</t>
         </is>
       </c>
     </row>
@@ -846,7 +846,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>13,94</t>
+          <t>9,99</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -861,7 +861,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>101,02%</t>
+          <t>53,7%</t>
         </is>
       </c>
     </row>
@@ -874,32 +874,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>5,16; 14,33</t>
+          <t>4,74; 14,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,52; 11,93</t>
+          <t>3,49; 11,8</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7,17; 25,04</t>
+          <t>5,92; 13,82</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>30,25; 126,87</t>
+          <t>31,81; 128,08</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>23,73; 100,33</t>
+          <t>22,11; 97,56</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,06; 360,68</t>
+          <t>28,51; 86,61</t>
         </is>
       </c>
     </row>
@@ -926,7 +926,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>11,95</t>
+          <t>12,28</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -941,7 +941,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>43,74%</t>
+          <t>45,73%</t>
         </is>
       </c>
     </row>
@@ -954,32 +954,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>12,49; 26,01</t>
+          <t>12,98; 26,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,36; 21,38</t>
+          <t>9,33; 21,6</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>7,29; 16,61</t>
+          <t>8,03; 16,37</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42,79; 116,32</t>
+          <t>44,11; 114,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>34,52; 105,46</t>
+          <t>33,91; 105,6</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,26; 68,63</t>
+          <t>26,3; 67,14</t>
         </is>
       </c>
     </row>
@@ -1006,7 +1006,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>2,4</t>
+          <t>18,77</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>66,82%</t>
         </is>
       </c>
     </row>
@@ -1034,32 +1034,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>3,31; 19,27</t>
+          <t>2,5; 18,4</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,76; 26,61</t>
+          <t>11,77; 26,38</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-16,17; 19,89</t>
+          <t>13,14; 23,95</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>6,02; 42,08</t>
+          <t>4,24; 39,09</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>31,61; 89,48</t>
+          <t>31,37; 88,73</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-53,22; 71,66</t>
+          <t>41,32; 96,05</t>
         </is>
       </c>
     </row>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25,24</t>
+          <t>25,1</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -1114,32 +1114,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>5,03; 19,38</t>
+          <t>4,16; 19,79</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3,86; 19,6</t>
+          <t>4,1; 19,63</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>19,73; 31,58</t>
+          <t>19,76; 30,41</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>7,07; 31,84</t>
+          <t>6,42; 32,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>6,84; 41,59</t>
+          <t>6,98; 41,42</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>42,65; 82,22</t>
+          <t>41,54; 75,68</t>
         </is>
       </c>
     </row>
@@ -1166,7 +1166,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>12,42</t>
+          <t>14,22</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>72,21%</t>
+          <t>78,37%</t>
         </is>
       </c>
     </row>
@@ -1194,32 +1194,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>10,23; 14,16</t>
+          <t>10,12; 14,24</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>8,87; 12,86</t>
+          <t>8,64; 12,72</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7,17; 15,97</t>
+          <t>12,39; 16,25</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>56,82; 88,56</t>
+          <t>55,85; 88,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>55,23; 91,31</t>
+          <t>54,63; 89,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>41,82; 109,93</t>
+          <t>64,79; 95,08</t>
         </is>
       </c>
     </row>
